--- a/Result/profitability/4938.xlsx
+++ b/Result/profitability/4938.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM71"/>
+  <dimension ref="A1:AM72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.46</v>
       </c>
       <c r="M2" t="n">
-        <v>1.18</v>
+        <v>1.18875</v>
       </c>
       <c r="N2" t="n">
-        <v>4.36125</v>
+        <v>4.40375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.27</v>
       </c>
       <c r="M3" t="n">
-        <v>1.0125</v>
+        <v>1.0475</v>
       </c>
       <c r="N3" t="n">
-        <v>4.29125</v>
+        <v>4.39375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.26</v>
       </c>
       <c r="M4" t="n">
-        <v>0.87</v>
+        <v>0.8775000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>4.162500000000001</v>
+        <v>4.25</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.87</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9012500000000001</v>
+        <v>1.0975</v>
       </c>
       <c r="N5" t="n">
-        <v>3.985</v>
+        <v>4.1475</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.97</v>
       </c>
       <c r="M6" t="n">
-        <v>1.00875</v>
+        <v>1.0075</v>
       </c>
       <c r="N6" t="n">
-        <v>4.635</v>
+        <v>4.66</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,13 +1264,13 @@
         <v>0.78</v>
       </c>
       <c r="M7" t="n">
-        <v>0.895</v>
+        <v>0.85875</v>
       </c>
       <c r="N7" t="n">
-        <v>4.915</v>
+        <v>4.9575</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.74</v>
       </c>
       <c r="M8" t="n">
-        <v>0.74125</v>
+        <v>0.8787499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>5.19375</v>
+        <v>5.194999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9445,6 +9445,133 @@
       </c>
       <c r="AM71" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>4938</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>274448</v>
+      </c>
+      <c r="D72" t="n">
+        <v>262292</v>
+      </c>
+      <c r="E72" t="n">
+        <v>12156</v>
+      </c>
+      <c r="F72" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="G72" t="n">
+        <v>4198</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>1.53%</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>3547</v>
+      </c>
+      <c r="J72" t="n">
+        <v>7744</v>
+      </c>
+      <c r="K72" t="n">
+        <v>4488</v>
+      </c>
+      <c r="L72" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1.3325</v>
+      </c>
+      <c r="N72" t="n">
+        <v>3.96625</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
+      </c>
+      <c r="V72" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W72" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X72" t="n">
+        <v>1.896551724137931</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0.002262443438914019</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>14.27272727272727</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>0.415335463258786</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK72" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
